--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B17890D5-B991-495B-A2C8-394A10999F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5588CB6-F2C7-4BB9-894E-F3A6BF90C412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2656,7 +2656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3238A1B9-E20B-43A3-BC69-2D1797B7E374}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53669FE7-BB52-4824-82C5-6AE7EB1579C5}">
   <dimension ref="B2:AF348"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8883,7 +8883,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A049CA3-0E7D-488F-A0BA-8E106A474811}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD45070-B140-4C95-9ED9-D5A5EE3D7B84}">
   <dimension ref="B9:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18070,7 +18070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72EB99E-E852-4799-A922-F29FC573E6A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA8B1291-0C15-4D92-B0B5-4177277E2666}">
   <dimension ref="A1:I77"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
